--- a/www/download/IND.gdp.s.us.rpO2.xlsx
+++ b/www/download/IND.gdp.s.us.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>352145.03092</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391906.39614</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>394570.53933</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>351456.9668</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>382442.57419</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>365788.02271</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347752.10647</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386739.55688</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498551.97846</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604453.0277</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>676492.62353</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>723227.09386</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>873935.04023</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>969504.49578</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>951503.773</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214794.56175</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209602.49665</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186128.57259</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191078.71824</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189166.22575</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172332.01223</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171989.39837</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186933.85264</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228522.03992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261156.17099</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272976.05059</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291936.03024</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337291.61221</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373596.9271</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>343199.74065</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256265.39088</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246996.40291</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223309.2975</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228500.90166</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226445.40076</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207317.35552</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207952.05864</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226718.0883</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279303.10468</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322369.35918</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335707.43775</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>355688.99926</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>409029.41653</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>453502.36311</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>423134.60351</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12315.32218</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12766.33026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9850.60101</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11412.73898</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11541.40971</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11171.40468</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12072.14785</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13634.0498</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17157.58343</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20644.92997</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22724.97905</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25973.50076</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33469.18166</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40790.5024</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39238.13703</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672761.72573</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739391.963</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>770856.21093</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>746739.55772</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514319.25099</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559147.93336</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>479213.823</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>450114.74325</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>480876.08161</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>570560.08381</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760113.6074</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935223.31104</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1175043.84655</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1407001.04657</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397589.07307</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>547035.37625</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569004.55983</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590028.93518</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571275.18468</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>612315.22592</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>673562.94928</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>666649.17545</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>681187.95021</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808003.50894</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>924738.04722</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1057277.28328</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1191310.6512</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1322736.20347</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1406788.2493</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1247760.13746</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>728004.9099</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>856112.02931</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>952651.77295</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1019495.10766</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1083298.8655</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1198412.56254</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1324853.7866</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1453859.59376</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1641010.55468</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1931650.10578</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>2257160.61468</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>2713231.49273</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>3495139.88151</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>4521311.96077</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4.984</t>
+          <t>4984441.76025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8457.07898</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8594.35449</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8252.77301</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8908.35267</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9137.40823</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8623.35115</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8904.39315</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9650.831</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12053.16323</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14275.94682</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15287.24424</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16510.99516</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19392.39255</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22483.38494</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21253.68265</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49985.45611</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55963.95023</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52086.50867</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56360.9167</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54454.00975</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51609.26447</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56102.60305</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68748.11483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83201.88235</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98632.14119</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111799.11835</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128896.57034</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157152.64045</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197451.80638</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171234.36262</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>2283990.57679</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>2207664.55777</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.959</t>
+          <t>1959437.56739</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.979</t>
+          <t>1979123.07082</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1929385.68507</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1714386.34745</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.706</t>
+          <t>1705661.28835</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.828</t>
+          <t>1828024.41557</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>2205172.50123</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2485759.88699</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2517921.49766</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>2635102.5568</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.989</t>
+          <t>2988690.39639</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.272</t>
+          <t>3272235.93379</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.986</t>
+          <t>2985722.71071</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157483.05634</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158438.14463</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146142.641</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147790.83357</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148173.76576</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137851.33465</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137855.44359</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149387.93264</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182658.11647</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209332.02582</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218631.31323</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232189.19251</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264102.73398</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294795.88113</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267929.10313</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550710.02026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>572844.64575</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>525357.19068</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>548410.88496</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559624.91495</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>526969.22874</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553706.49973</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>625530.45648</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>799681.45405</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>941220.52479</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012418.70097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1100942.70418</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1294881.26226</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1464933.02076</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1366484.11401</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3328.88604</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4171.19585</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4422.00556</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4982.86686</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5140.18771</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5090.12008</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5563.42507</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6535.17728</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8804.27792</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10653.95152</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12322.90053</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14775.72882</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18971.75527</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21047.2485</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16677.98605</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114210.78898</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111587.58034</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106259.14314</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112361.97238</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112708.34567</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106274.95992</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109167.37247</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118529.06536</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142702.00502</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164832.91296</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170018.7025</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180375.72569</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215108.19305</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237540.08998</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207610.39301</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1405135.00538</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1402022.24263</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1271429.18983</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>1314179.58154</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1300257.80852</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1192130.26634</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1204275.74037</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1316829.28065</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1623059.28313</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1853697.00974</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.926</t>
+          <t>1925565.68794</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>2026966.52079</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2327698.26091</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.575</t>
+          <t>2574694.1485</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2401496.78398</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1047516.88555</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1100347.37222</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1217407.20315</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1310780.13128</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1343247.17625</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325745.66129</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1319582.23015</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1458373.53539</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1684919.42233</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>2004599.18394</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>2072674.67191</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2224544.26258</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>2556704.64799</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>2451685.96675</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>2008379.50882</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119108.02389</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125146.52611</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121450.04542</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122416.00866</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124289.05839</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112669.29529</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115504.25248</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131547.85645</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174547.54951</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207159.07592</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217249.25647</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234465.03948</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>274145.13524</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308371.0351</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>293751.9468</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38822.70562</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39812.98837</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40882.20149</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42094.77933</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42156.82068</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40596.62111</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46110.18784</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58054.85829</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71953.48274</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87733.03472</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94502.09813</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97659.88552</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118196.31486</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134007.94333</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109022.23903</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241322.3402</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277829.60168</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278513.12934</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110254.93203</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162975.33114</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174137.53357</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169380.39744</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204960.11188</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241640.94758</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252540.88321</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>277428.10328</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367313.84899</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434598.26157</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514114.22125</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>543699.98896</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>349731.10678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>371626.51384</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403751.8001</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>409164.34606</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>435287.43814</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>448078.92678</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>463766.18702</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485869.89049</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>570083.9474</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>663677.56102</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>781394.70339</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>881604.07887</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114065.82189</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>1224635.4291</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1257941.60896</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60022.68979</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66280.82996</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72399.69906</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79983.52148</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86090.13958</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86506.48093</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93933.0676</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109735.79788</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140279.43178</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163387.89782</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176852.83901</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195477.08037</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>227784.1037</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235017.96679</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>202200.53198</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>1015224.48048</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1138351.28003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1072755.50759</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1089346.37111</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1071561.77273</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>982743.9463</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1005738.36098</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1102019.91237</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1361670.33448</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1557387.80676</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1597977.03485</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1663394.21691</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1895232.04848</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>2072559.02902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.908</t>
+          <t>1907704.10972</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5239622.30643</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>4607107.94388</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4227253.67291</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>3848023.03888</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.353</t>
+          <t>4353164.29961</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.637</t>
+          <t>4637061.77664</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.048</t>
+          <t>4048376.41371</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.886</t>
+          <t>3886434.32292</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>4199314.51041</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4.555</t>
+          <t>4554544.73269</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4.528</t>
+          <t>4528208.93205</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.309</t>
+          <t>4309123.01772</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>4310707.20875</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4.786</t>
+          <t>4785564.42746</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4.915</t>
+          <t>4915208.0621</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>481503.17054</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514093.81342</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485541.05132</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328004.00125</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>413467.1516</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>473921.91525</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446063.37838</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>510694.51224</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>573050.25274</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>645393.89376</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760371.80792</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855420.37031</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>944764.49479</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850591.90201</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>754935.69005</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6015.75001</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7580.42491</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8877.82507</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9865.37498</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9643.52504</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10150.42498</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10812.65001</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12624.41969</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16684.51923</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20405.27723</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23527.31855</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27157.11095</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35081.64431</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42587.50494</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33266.37896</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18735.43524</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18683.3784</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16670.597</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17399.10317</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19000.33556</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18124.08023</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18156.49922</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20370.30339</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26284.10943</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30463.2337</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33681.64341</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38376.15784</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46333.3156</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52737.44736</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48032.30699</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4361.5605</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5029.91232</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5531.07297</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5903.75351</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6486.13701</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7020.4796</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7489.45788</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8399.4092</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10005.89694</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12335.1303</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14240.84683</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17566.34487</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25453.29368</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30342.02577</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23376.71382</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309604.04105</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353868.96391</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>423390.78749</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448565.25097</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>509870.85234</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>609306.68471</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>648132.70032</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>682132.37731</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>664418.82444</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>724204.13104</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>810142.74071</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912676.53596</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>993284.61855</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1073095.15612</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>840456.68997</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3197.71274</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3308.85405</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3245.0926</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3439.99494</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3473.64834</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3454.01761</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3389.1217</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3747.28687</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4407.92382</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4884.07563</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5167.44378</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5505.79668</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6530.86134</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7612.71384</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7102.18183</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378720.87595</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>375384.50507</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346649.61493</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>360457.34849</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>366992.22751</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>344886.09982</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356051.16282</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391832.04487</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>481049.56634</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>543427.54301</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>567536.01462</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>601447.45552</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695734.30904</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>778522.40752</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>710816.55455</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122640.12956</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138034.17251</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139287.39404</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153737.52323</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148163.80081</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152616.14468</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169906.41451</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175335.64936</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191478.3927</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225809.97583</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268059.51017</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300361.1119</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>373265.35935</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>469598.74988</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385537.9964</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99057.6502</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102846.15286</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98124.56926</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103270.58906</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105504.92153</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98404.87161</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101039.08849</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111345.05962</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136270.34256</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155873.3504</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159696.1551</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170764.98813</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199678.96806</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219403.16385</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205647.15759</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35877.50728</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35199.14063</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33508.59582</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37587.07337</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32607.53665</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33927.16623</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36641.11243</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41431.32064</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52915.33532</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67832.53525</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87708.16531</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108487.40076</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151298.66226</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183466.00776</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147247.23002</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>315027.98855</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>375238.82981</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382611.49572</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>303478.02436</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176791.14595</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232582.24198</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273751.29267</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311717.26539</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378803.84853</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515747.82766</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>654784.67717</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>845566.25962</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114312.52825</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1428383.26757</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1081377.73784</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17566.14321</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19043.80717</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19317.23338</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20054.75071</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18161.81472</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18263.40166</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19101.92054</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22172.76054</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29857.22044</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37727.11365</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42616.71973</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50521.7945</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67858.66595</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86138.38143</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79973.46762</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17824.08937</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18025.64887</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17788.21641</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18671.39514</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19089.91386</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17406.2795</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17851.20702</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20129.5912</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25395.87408</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29530.84924</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31391.99891</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34190.18563</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41582.991</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48155.7669</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43055.07032</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221026.57373</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241622.0427</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222083.29063</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222828.18396</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226402.71934</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217884.4608</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199620.81731</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220412.1077</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276351.35181</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>318235.78453</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>325155.99724</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350022.82136</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405845.0917</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>431154.64321</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353704.9024</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>210799.46371</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231384.94676</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244175.24729</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252531.94134</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239005.73626</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250821.76909</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189715.63136</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205168.44958</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266159.45176</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338865.30422</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>418626.86591</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461990.55552</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571402.96677</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>652173.05298</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544892.25681</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261668.59049</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278192.56237</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289140.826</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>266543.60649</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289071.71928</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>310928.06522</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>283348.98154</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288743.47734</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296373.44758</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>320931.3513</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>345206.33178</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>355567.8303</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373773.77237</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380353.52593</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357822.52825</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7.421</t>
+          <t>7421307.28983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>7845492.08402</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8.336</t>
+          <t>8336460.34793</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>8.791</t>
+          <t>8791210.05959</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9.351</t>
+          <t>9351440.43509</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9950000.79912</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>10284231.01067</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>10.641</t>
+          <t>10640630.70387</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11.138</t>
+          <t>11137509.03847</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>11.866</t>
+          <t>11866059.87271</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>12.637</t>
+          <t>12636578.55469</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>13.396</t>
+          <t>13396348.08839</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>14059789.88234</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>14367832.91431</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>14.117</t>
+          <t>14116979.99525</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3100061.91984787</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3310373.4744688</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3370415.8176897</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3.221</t>
+          <t>3221261.55108232</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.257</t>
+          <t>3257066.93491647</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>3398413.01767922</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>3375819.90928846</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>3352394.52778614</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3.736</t>
+          <t>3736360.3239901</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>4357033.25331906</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5050013.08052761</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>5791309.48199016</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6.786</t>
+          <t>6786121.13592133</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>8.286</t>
+          <t>8285953.90396788</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>7706866.58207004</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28.493</t>
+          <t>28492989.6170379</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.147</t>
+          <t>29146972.6201288</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.078</t>
+          <t>29078015.2833797</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28.869</t>
+          <t>28868950.3097123</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29.949</t>
+          <t>29949423.6708065</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30.886</t>
+          <t>30886319.2747992</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30.695</t>
+          <t>30695232.7155385</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>31.979</t>
+          <t>31978700.6609161</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>35.759</t>
+          <t>35758542.8815301</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40119766.8033391</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>43.347</t>
+          <t>43347211.2731476</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>46.869</t>
+          <t>46869212.7940502</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>52.756</t>
+          <t>52756188.9207813</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>58.372</t>
+          <t>58371735.6131579</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>55.504</t>
+          <t>55504275.79824</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
